--- a/erp-server/erp-server-plm/src/main/resources/excel/moldInfoTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/moldInfoTemplate.xlsx
@@ -30,6 +30,13 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -45,6 +52,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -63,6 +77,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -78,6 +99,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -96,6 +124,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -111,6 +146,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -126,6 +168,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -140,7 +189,23 @@
     </r>
   </si>
   <si>
-    <r>
+    <t>模具长(mm)</t>
+  </si>
+  <si>
+    <t>模具宽(mm)</t>
+  </si>
+  <si>
+    <t>模具高(mm)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -151,11 +216,18 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>模具长(mm)</t>
-    </r>
-  </si>
-  <si>
-    <r>
+      <t>模具材质</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -166,11 +238,18 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>模具宽(mm)</t>
-    </r>
-  </si>
-  <si>
-    <r>
+      <t>开模周期(自然日)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -181,11 +260,18 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>模具高(mm)</t>
-    </r>
-  </si>
-  <si>
-    <r>
+      <t>模具启用日期</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -196,11 +282,21 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>模具材质</t>
-    </r>
-  </si>
-  <si>
-    <r>
+      <t>供应商</t>
+    </r>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -211,11 +307,18 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>开模周期(自然日)</t>
-    </r>
-  </si>
-  <si>
-    <r>
+      <t>含税单价</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -226,11 +329,18 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>模具启用日期</t>
-    </r>
-  </si>
-  <si>
-    <r>
+      <t>税率(%)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -241,59 +351,18 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>供应商</t>
-    </r>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>含税单价</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>税率(%)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>结算方式</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -928,7 +997,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -936,6 +1005,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1290,13 +1362,13 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="2" t="s">

--- a/erp-server/erp-server-plm/src/main/resources/excel/moldInfoTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/moldInfoTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <r>
       <rPr>
@@ -287,94 +287,6 @@
   </si>
   <si>
     <t>备注</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>含税单价</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>税率(%)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>结算方式</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>付款条件</t>
-    </r>
   </si>
 </sst>
 </file>
@@ -1321,7 +1233,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
@@ -1331,10 +1243,10 @@
     <col min="5" max="9" width="9" style="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
     <col min="11" max="11" width="11.5" style="1" customWidth="1"/>
-    <col min="12" max="21" width="9" style="1"/>
+    <col min="12" max="17" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1385,18 +1297,6 @@
       </c>
       <c r="Q1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-plm/src/main/resources/excel/moldInfoTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/moldInfoTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <r>
       <rPr>
@@ -287,6 +287,94 @@
   </si>
   <si>
     <t>备注</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>含税单价</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>税率(%)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>结算方式</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>付款条件</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1233,7 +1321,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
@@ -1243,10 +1331,10 @@
     <col min="5" max="9" width="9" style="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
     <col min="11" max="11" width="11.5" style="1" customWidth="1"/>
-    <col min="12" max="17" width="9" style="1"/>
+    <col min="12" max="21" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:21">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1297,6 +1385,18 @@
       </c>
       <c r="Q1" s="1" t="s">
         <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
